--- a/data/compound_identification.xlsx
+++ b/data/compound_identification.xlsx
@@ -1005,7 +1005,7 @@
         <v>19</v>
       </c>
       <c r="D17" s="2">
-        <v>1269.97</v>
+        <v>1269.79</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
